--- a/docs/测试/03-BUG记录与汇总表.xlsx
+++ b/docs/测试/03-BUG记录与汇总表.xlsx
@@ -739,11 +739,11 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>OBS-001 ~ OBS-010，见「观察项与建议」表</t>
+          <t>OBS-001 ~ OBS-013，见「观察项与建议」表</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1554,6 +1554,117 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="78" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>OBS-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>卖家账号</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>需求要求新密码不少于 8 位，后端实现仅要求 6 位</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>需求 FR-035 / FR-041 明确「新密码长度不少于 8 位」；后端 schemas.py 中 ChangePasswordRequest.new_password 仅约束 min_length=6。长度为 6~7 位的新密码会被后端接受，违反需求。</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>代码核对 backend/app/schemas.py（min_length=6）；需求依据 Requirement Analysis/需求规格说明书.md 第 4.5 节 FR-035 / FR-041。</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>将后端校验收紧为 min_length=8，并同步前端改密页的校验提示；补充「6~7 位新密码应被拒绝」的测试用例。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="78" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>OBS-012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>文件上传</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>需求要求图片仅支持 JPG/PNG，后端实现额外允许 GIF/WebP</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>需求 FR-001 / FR-036 与 NFR-012 明确「仅支持 JPG/PNG 格式，单张 ≤5MB」；后端 config.py 的 ALLOWED_IMAGE_EXT 为 {.jpg, .jpeg, .png, .gif, .webp}，gif 与 webp 会被接受，超出需求范围。</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>代码核对 backend/app/config.py；需求依据 Requirement Analysis/需求规格说明书.md FR-001 / FR-036、NFR-012。</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>若确认仅需 JPG/PNG，将白名单收紧为 {.jpg, .jpeg, .png}；若需保留 GIF/WebP，则应修订需求。二者取一，避免需求与实现长期不一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="78" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>OBS-013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>历史记录</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>需求要求历史列表可筛选，接口仅实现关键词检索</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>需求 FR-004 / FR-037 要求历史商品列表「可分页、可检索、可筛选」；后端 GET /api/seller/history 仅提供 keyword 模糊检索与分页参数，无状态筛选参数，前端也无筛选控件。</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>代码核对 backend/app/routers/seller.py 与 product_service.list_history()；需求依据 Requirement Analysis/需求规格说明书.md FR-004 / FR-037。</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>为历史列表补充 status 筛选参数并在前端增加筛选控件；或将需求修订为「可分页、可检索」。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/测试/03-BUG记录与汇总表.xlsx
+++ b/docs/测试/03-BUG记录与汇总表.xlsx
@@ -719,11 +719,11 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>2 / 113 × 100</t>
+          <t>2 / 117 × 100</t>
         </is>
       </c>
     </row>
